--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -5693,23 +5693,19 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>3728000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>22190</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5718,12 +5714,12 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
@@ -5733,7 +5729,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7136,7 +7132,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7146,7 +7142,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7203,7 +7199,7 @@
           <t>A | 250呎 (开放式)
 $675万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -7211,7 +7207,7 @@
           <t>B | 246呎 (1房)
 $664万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -7219,7 +7215,7 @@
           <t>C | 272呎 (1房)
 $734万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -7228,7 +7224,7 @@
           <t>E | 203呎 (开放式)
 $548万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7239,7 @@
           <t>A | 250呎 (开放式)
 $675万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7251,7 +7247,7 @@
           <t>B | 246呎 (1房)
 $664万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7259,7 +7255,7 @@
           <t>C | 272呎 (1房)
 $734万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -7268,7 +7264,7 @@
           <t>E | 203呎 (开放式)
 $548万
 $27,000/呎
-(26年-09月-01日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -7907,12 +7903,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
+$373万
+$22,190/呎
+(26年-09月-07日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -4655,23 +4655,19 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>3878000</v>
+      </c>
+      <c r="I59" s="5" t="n">
+        <v>23083</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4680,12 +4676,12 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -4695,7 +4691,7 @@
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4936,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -7132,7 +7128,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7142,7 +7138,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7735,7 +7731,7 @@
           <t>A | 243呎 (开放式)
 $562万
 $23,119/呎
-(26年-08月-29日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7762,12 +7758,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
+$388万
+$23,083/呎
+(26年-09月-08日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -6171,23 +6171,19 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>22920</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -6196,12 +6192,12 @@
       </c>
       <c r="K81" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -6211,7 +6207,7 @@
       </c>
       <c r="N81" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6381,23 +6377,19 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>3628000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>27908</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -6406,12 +6398,12 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
@@ -6421,7 +6413,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7120,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7138,7 +7130,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7930,12 +7922,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+$399万
+$22,920/呎
+(26年-09月-13日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -7993,12 +7985,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 130呎 (开放式)
-招标单位
--
-(在售)</t>
+$363万
+$27,908/呎
+(26年-09月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>开放式</t>
+          <t>1房</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>C | 272呎 (开放式)
+          <t>C | 272呎 (1房)
 -
 -
 (待售)</t>
@@ -7794,7 +7794,7 @@
           <t>D | 176呎 (开放式)
 $418万
 $23,750/呎
-(26年-08月-30日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -7802,7 +7802,7 @@
           <t>E | 168呎 (开放式)
 $383万
 $22,786/呎
-(26年-08月-30日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -5694,7 +5694,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -6443,23 +6443,19 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>3980000</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>22614</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6468,12 +6464,12 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
@@ -6483,7 +6479,7 @@
       </c>
       <c r="N85" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6513,23 +6509,19 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>3938000</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>22632</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -6538,12 +6530,12 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M86" s="3" t="inlineStr">
@@ -6553,7 +6545,7 @@
       </c>
       <c r="N86" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7112,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7130,7 +7122,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7896,7 +7888,7 @@
           <t>E | 168呎 (开放式)
 $373万
 $22,190/呎
-(26年-09月-07日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7935,7 @@
           <t>E | 168呎 (开放式)
 $368万
 $21,893/呎
-(26年-08月-31日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
     </row>
@@ -7969,20 +7961,20 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="22" t="inlineStr">
+$394万
+$22,632/呎
+(26年-09月-18日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
+$398万
+$22,614/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,12 +121,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -207,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -272,10 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -772,7 +763,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -838,7 +829,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -904,7 +895,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -970,7 +961,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1027,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1102,7 +1093,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1168,7 +1159,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1234,7 +1225,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1295,7 +1286,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1305,12 +1296,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1320,12 +1311,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1335,7 +1326,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1356,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1375,12 +1366,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1390,12 +1381,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1405,7 +1396,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1426,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1445,12 +1436,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1460,12 +1451,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1475,7 +1466,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1496,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1515,12 +1506,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1530,12 +1521,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1545,7 +1536,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4712,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4731,12 +4722,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4746,12 +4737,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4761,7 +4752,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4782,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4801,12 +4792,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -4816,12 +4807,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4831,7 +4822,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4852,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4871,12 +4862,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -4886,12 +4877,12 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4901,7 +4892,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5120,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5139,12 +5130,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -5154,12 +5145,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5169,7 +5160,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5190,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5209,12 +5200,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -5224,12 +5215,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -5239,7 +5230,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5260,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5279,12 +5270,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -5294,12 +5285,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -5309,7 +5300,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5746,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5765,12 +5756,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5780,12 +5771,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5795,7 +5786,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5816,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5835,12 +5826,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -5850,12 +5841,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5865,7 +5856,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5886,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5905,12 +5896,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -5920,12 +5911,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5935,7 +5926,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5956,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5975,12 +5966,12 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -5990,12 +5981,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -6005,7 +5996,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6101,23 +6092,19 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>22727</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -6126,12 +6113,12 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -6141,7 +6128,7 @@
       </c>
       <c r="N80" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6176,7 +6163,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6237,7 +6224,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6247,12 +6234,12 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -6262,12 +6249,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6277,7 +6264,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6294,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6317,12 +6304,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -6332,12 +6319,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6347,7 +6334,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6562,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6585,12 +6572,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -6600,12 +6587,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -6615,7 +6602,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6632,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6655,12 +6642,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -6670,12 +6657,12 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -6685,7 +6672,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7112,27 +7099,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7166,7 @@
           <t>A | 250呎 (开放式)
 $675万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -7187,7 +7174,7 @@
           <t>B | 246呎 (1房)
 $664万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -7195,7 +7182,7 @@
           <t>C | 272呎 (1房)
 $734万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr"/>
@@ -7204,7 +7191,7 @@
           <t>E | 203呎 (开放式)
 $548万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7206,7 @@
           <t>A | 250呎 (开放式)
 $675万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -7227,7 +7214,7 @@
           <t>B | 246呎 (1房)
 $664万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -7235,7 +7222,7 @@
           <t>C | 272呎 (1房)
 $734万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -7244,7 +7231,7 @@
           <t>E | 203呎 (开放式)
 $548万
 $27,000/呎
-(26年-09月-02日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -7257,34 +7244,34 @@
       <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 246呎 (1房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 272呎 (1房)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr"/>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7281,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
 -
@@ -7302,7 +7289,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 246呎 (1房)
 -
@@ -7310,7 +7297,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 272呎 (1房)
 -
@@ -7319,7 +7306,7 @@
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
 -
@@ -7334,7 +7321,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7342,7 +7329,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7350,7 +7337,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7358,7 +7345,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7366,7 +7353,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7381,7 +7368,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7389,7 +7376,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7397,7 +7384,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7405,7 +7392,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7413,7 +7400,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7428,7 +7415,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7436,7 +7423,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7444,7 +7431,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7452,7 +7439,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7460,7 +7447,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7475,7 +7462,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7483,7 +7470,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7491,7 +7478,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7499,7 +7486,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7507,7 +7494,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7522,7 +7509,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7530,7 +7517,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7538,7 +7525,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7546,7 +7533,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7554,7 +7541,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7569,7 +7556,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7577,7 +7564,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7585,7 +7572,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7593,7 +7580,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7601,7 +7588,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7616,7 +7603,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7624,7 +7611,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7632,7 +7619,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7640,7 +7627,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7648,7 +7635,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7663,7 +7650,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7671,7 +7658,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7679,7 +7666,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7687,7 +7674,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7695,7 +7682,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7721,25 +7708,25 @@
       <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -7760,25 +7747,25 @@
       <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7804,7 +7791,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7812,7 +7799,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7820,7 +7807,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7828,7 +7815,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7836,7 +7823,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7854,33 +7841,33 @@
       <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -7901,17 +7888,17 @@
       <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7919,15 +7906,15 @@
           <t>C | 174呎 (开放式)
 $399万
 $22,920/呎
-(26年-09月-13日)</t>
-        </is>
-      </c>
-      <c r="E21" s="22" t="inlineStr">
+(26年-10月-05日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
+$400万
+$22,727/呎
+(26年-09月-29日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -7948,17 +7935,17 @@
       <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 187呎 (开放式)
-招标单位
--
-(在售)</t>
+-
+-
+(待售)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7992,7 +7979,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 206呎 (开放式)
 -
@@ -8000,7 +7987,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 221呎 (开放式)
 -
@@ -8008,7 +7995,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 144呎 (开放式)
 -
@@ -8016,7 +8003,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 146呎 (开放式)
 -
@@ -8024,7 +8011,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 165呎 (开放式)
 -

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -7734,7 +7734,7 @@
           <t>E | 168呎 (开放式)
 $388万
 $23,083/呎
-(26年-09月-08日)</t>
+(26年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
           <t>C | 174呎 (开放式)
 $394万
 $22,632/呎
-(26年-09月-18日)</t>
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -121,6 +121,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
@@ -201,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,7 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1286,7 +1295,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1296,12 +1305,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1311,12 +1320,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1326,7 +1335,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1365,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1366,12 +1375,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1381,12 +1390,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1396,7 +1405,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1435,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1436,12 +1445,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1451,12 +1460,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1466,7 +1475,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1505,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1506,12 +1515,12 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1521,12 +1530,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1536,7 +1545,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4721,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4722,12 +4731,12 @@
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -4737,12 +4746,12 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -4752,7 +4761,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4792,12 +4801,12 @@
       </c>
       <c r="H61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -4807,12 +4816,12 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -4822,7 +4831,7 @@
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4861,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -4862,12 +4871,12 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -4877,12 +4886,12 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -4892,7 +4901,7 @@
       </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5129,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -5130,12 +5139,12 @@
       </c>
       <c r="H66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -5145,12 +5154,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5160,7 +5169,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5199,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -5200,12 +5209,12 @@
       </c>
       <c r="H67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -5215,12 +5224,12 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -5230,7 +5239,7 @@
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5269,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -5270,12 +5279,12 @@
       </c>
       <c r="H68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -5285,12 +5294,12 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
@@ -5300,7 +5309,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5746,7 +5755,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -5756,12 +5765,12 @@
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr">
@@ -5771,12 +5780,12 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -5786,7 +5795,7 @@
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5825,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -5826,12 +5835,12 @@
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -5841,12 +5850,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5856,7 +5865,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5895,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -5896,12 +5905,12 @@
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J77" s="3" t="inlineStr">
@@ -5911,12 +5920,12 @@
       </c>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -5926,7 +5935,7 @@
       </c>
       <c r="N77" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5965,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -5966,12 +5975,12 @@
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -5981,12 +5990,12 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -5996,7 +6005,7 @@
       </c>
       <c r="N78" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6233,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -6234,12 +6243,12 @@
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -6249,12 +6258,12 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
@@ -6264,7 +6273,7 @@
       </c>
       <c r="N82" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6303,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6304,12 +6313,12 @@
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -6319,12 +6328,12 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
@@ -6334,7 +6343,7 @@
       </c>
       <c r="N83" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6571,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -6572,12 +6581,12 @@
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J87" s="3" t="inlineStr">
@@ -6587,12 +6596,12 @@
       </c>
       <c r="K87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L87" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M87" s="3" t="inlineStr">
@@ -6602,7 +6611,7 @@
       </c>
       <c r="N87" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6641,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6642,12 +6651,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -6657,12 +6666,12 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -6672,7 +6681,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7099,27 +7108,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>54</t>
         </is>
       </c>
     </row>
@@ -7244,34 +7253,34 @@
       <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 246呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 272呎 (1房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr"/>
       <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7290,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
 -
@@ -7289,7 +7298,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 246呎 (1房)
 -
@@ -7297,7 +7306,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 272呎 (1房)
 -
@@ -7306,7 +7315,7 @@
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
 -
@@ -7321,7 +7330,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7329,7 +7338,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7337,7 +7346,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7345,7 +7354,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7353,7 +7362,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7368,7 +7377,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7376,7 +7385,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7384,7 +7393,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7392,7 +7401,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7400,7 +7409,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7415,7 +7424,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7423,7 +7432,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7431,7 +7440,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7439,7 +7448,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7447,7 +7456,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7462,7 +7471,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7470,7 +7479,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7478,7 +7487,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7486,7 +7495,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7494,7 +7503,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7509,7 +7518,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7517,7 +7526,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7525,7 +7534,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7533,7 +7542,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7541,7 +7550,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7556,7 +7565,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7564,7 +7573,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7572,7 +7581,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7580,7 +7589,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7588,7 +7597,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7603,7 +7612,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7611,7 +7620,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7619,7 +7628,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7627,7 +7636,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7635,7 +7644,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7650,7 +7659,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7658,7 +7667,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7666,7 +7675,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7674,7 +7683,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7682,7 +7691,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7708,25 +7717,25 @@
       <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -7747,25 +7756,25 @@
       <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7791,7 +7800,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 -
@@ -7799,7 +7808,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 -
@@ -7807,7 +7816,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 -
@@ -7815,7 +7824,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 -
@@ -7823,7 +7832,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 -
@@ -7841,33 +7850,33 @@
       <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -7888,17 +7897,17 @@
       <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7935,17 +7944,17 @@
       <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 187呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7979,7 +7988,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 206呎 (开放式)
 -
@@ -7987,7 +7996,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 221呎 (开放式)
 -
@@ -7995,7 +8004,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 144呎 (开放式)
 -
@@ -8003,7 +8012,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 146呎 (开放式)
 -
@@ -8011,7 +8020,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 165呎 (开放式)
 -

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -6378,7 +6378,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -7970,7 +7970,7 @@
           <t>D | 176呎 (开放式)
 $398万
 $22,614/呎
-(26年-09月-19日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -7978,7 +7978,7 @@
           <t>E | 130呎 (开放式)
 $363万
 $27,908/呎
-(26年-09月-13日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="H69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J89" s="3" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="K89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M89" s="3" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="N89" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J90" s="3" t="inlineStr">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M90" s="3" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="N90" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="K91" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L91" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M91" s="3" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="N91" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>50</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -8004,28 +8004,28 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 144呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 146呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="23" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 165呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -5129,23 +5129,19 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>4138000</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>23782</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -5154,12 +5150,12 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -5169,7 +5165,7 @@
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5339,23 +5335,19 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>22619</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -5364,12 +5356,12 @@
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -5379,7 +5371,7 @@
       </c>
       <c r="N69" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5825,23 +5817,19 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>4038000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>23207</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5850,12 +5838,12 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -5865,7 +5853,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6106,7 +6094,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -7108,27 +7096,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -7315,12 +7303,12 @@
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr"/>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7757,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+$414万
+$23,782/呎
+(26年-10月-25日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -7832,12 +7820,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
+$380万
+$22,619/呎
+(26年-10月-22日)</t>
         </is>
       </c>
     </row>
@@ -7863,12 +7851,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
+$404万
+$23,207/呎
+(26年-10月-17日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -7923,7 +7911,7 @@
           <t>D | 176呎 (开放式)
 $400万
 $22,727/呎
-(26年-09月-29日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
